--- a/tests/fixtures/check/IREX_Rehab_Data_Collection_CY2025 – ID lookup.xlsx
+++ b/tests/fixtures/check/IREX_Rehab_Data_Collection_CY2025 – ID lookup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,34 +781,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TD-0001</t>
+          <t>MED-0005</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Talent Development</t>
-        </is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Test Fellowship Award</t>
+          <t>Therapy tips video</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tan Wei Ling</t>
+          <t>Therapy tips video</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Test Fellowship Award</t>
+          <t>TestTube</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TD-0002</t>
+          <t>TD-0001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -818,24 +821,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Test Teaching Award</t>
+          <t>Test Fellowship Award</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Goh Mei Xin</t>
+          <t>Tan Wei Ling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Test Teaching Award</t>
+          <t>Test Fellowship Award</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TD-0003</t>
+          <t>TD-0002</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -845,49 +848,51 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Test Nursing Award</t>
+          <t>Test Teaching Award</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lee Hui Min</t>
+          <t>Goh Mei Xin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Test Nursing Award</t>
+          <t>Test Teaching Award</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EDU-0001</t>
+          <t>TD-0003</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Talent Development</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Spasticity workshop</t>
+          <t>Test Nursing Award</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spasticity workshop</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>2025</v>
+          <t>Lee Hui Min</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Test Nursing Award</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EDU-0002</t>
+          <t>EDU-0001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -897,19 +902,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pressure injury prevention webinar</t>
+          <t>Spasticity workshop</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pressure injury prevention webinar</t>
-        </is>
+          <t>Spasticity workshop</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EDU-0003</t>
+          <t>EDU-0002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -919,22 +927,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Caregiver training sharing</t>
+          <t>Pressure injury prevention webinar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Caregiver training sharing</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>2025</v>
+          <t>Pressure injury prevention webinar</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EDU-0004</t>
+          <t>EDU-0003</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -944,83 +949,81 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hand therapy splinting course</t>
+          <t>Caregiver training sharing</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hand therapy splinting course</t>
-        </is>
+          <t>Caregiver training sharing</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EDU-0005</t>
+          <t>EDU-0004</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Education</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hand therapy splinting course</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Hand therapy splinting course</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EDU-0006</t>
+          <t>EDU-0005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Community rehab workshop</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Community rehab workshop</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PRJ-0001</t>
+          <t>EDU-0006</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Robot-assisted gait study</t>
+          <t>Community rehab workshop</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GRT-001</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Robot-assisted gait study</t>
-        </is>
+          <t>Community rehab workshop</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRJ-0002</t>
+          <t>PRJ-0001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1030,24 +1033,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Home exercise app</t>
+          <t>Robot-assisted gait study</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GRT-002</t>
+          <t>GRT-001</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Home exercise app</t>
+          <t>Robot-assisted gait study</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRJ-0003</t>
+          <t>PRJ-0002</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1057,24 +1060,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Community stroke registry</t>
+          <t>Home exercise app</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GRT-005</t>
+          <t>GRT-002</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Community stroke registry</t>
+          <t>Home exercise app</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRJ-0004</t>
+          <t>PRJ-0003</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1084,19 +1087,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Exoskeleton feasibility</t>
+          <t>Community stroke registry</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GRT-005</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Exoskeleton feasibility</t>
+          <t>Community stroke registry</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PRJ-0005</t>
+          <t>PRJ-0004</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1106,42 +1114,64 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Regional falls network</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>GRT-007</t>
+          <t>Exoskeleton feasibility</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Regional falls network</t>
+          <t>Exoskeleton feasibility</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>PRJ-0005</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Regional falls network</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GRT-007</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Regional falls network</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>PRJ-0006</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Pressure mapping pilot</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>GRT-009</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Pressure mapping pilot</t>
         </is>
